--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2454-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2454-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18FB3B85-FD24-4DFC-B041-EE2F7B7FB3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C12BC07C-B370-41B6-A076-C397DDF13ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{BC7A125E-DEB3-45A2-8848-DE45D93EC1B4}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D234AC18-C547-4AB0-8214-98D97ACD85EE}"/>
   </bookViews>
   <sheets>
     <sheet name="2454-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1570,30 +1570,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D3ADD2-E6A9-44CB-8677-90DE0A3DF440}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3824145-8EF2-45DA-9D0A-5C8C9BC4E675}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1627,7 +1627,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1663,7 +1663,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1783,7 +1783,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1891,7 +1891,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="49">
         <v>2024</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>30</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="51">
         <v>2023</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>6.26</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>30</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="49">
         <v>2022</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="51">
         <v>2021</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="49">
         <v>2020</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="51">
         <v>2019</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="49">
         <v>2018</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="51">
         <v>2017</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="49">
         <v>2016</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="51">
         <v>2015</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="49">
         <v>2014</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>9.69</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="51">
         <v>2013</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="49">
         <v>2012</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="51">
         <v>2011</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="49">
         <v>2010</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="51">
         <v>2009</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="49">
         <v>2008</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="51">
         <v>2007</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="49">
         <v>2006</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="51">
         <v>2005</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="49">
         <v>2004</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="51">
         <v>2003</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="49">
         <v>2002</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="51">
         <v>2001</v>
       </c>
@@ -3989,7 +3989,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="49">
         <v>2000</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="51">
         <v>1999</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="49" t="s">
         <v>61</v>
       </c>
